--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5075" uniqueCount="840">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1801,7 +1801,7 @@
     <t>A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260916095453</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -2429,7 +2429,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Autorisation de substitution</t>
+    <t>Autorisation de substitution / non-substitution</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -2480,7 +2480,7 @@
     <t>allowedCodeableConcept</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis|20260916095455</t>
   </si>
   <si>
     <t>MedicationRequest.substitution.reason</t>
@@ -2492,10 +2492,7 @@
     <t>Indicates the reason for the substitution, or why substitution must or must not be performed.</t>
   </si>
   <si>
-    <t>A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-substitution-medicament-prescripteur-cisis|20260916095453</t>
   </si>
   <si>
     <t>not mapped</t>
@@ -18084,13 +18081,11 @@
         <v>81</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y130" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y130" s="2"/>
+      <c r="Z130" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>81</v>
@@ -18126,24 +18121,24 @@
         <v>81</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="AM130" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="AM130" t="s" s="2">
+      <c r="AN130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO130" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>801</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18255,10 +18250,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18372,10 +18367,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18398,19 +18393,19 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>807</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18459,7 +18454,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18480,21 +18475,21 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO133" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>812</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18520,16 +18515,16 @@
         <v>369</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>815</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -18578,7 +18573,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18599,21 +18594,21 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>820</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18636,13 +18631,13 @@
         <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18693,7 +18688,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18708,13 +18703,13 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -18725,14 +18720,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18751,16 +18746,16 @@
         <v>81</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>829</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18810,7 +18805,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18831,7 +18826,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18842,10 +18837,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18868,16 +18863,16 @@
         <v>81</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>835</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18927,7 +18922,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18942,13 +18937,13 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
